--- a/RESULTS/tables/decision_curve_external_validation.xlsx
+++ b/RESULTS/tables/decision_curve_external_validation.xlsx
@@ -481,7 +481,7 @@
         <v>0.05</v>
       </c>
       <c r="C4" t="n">
-        <v>0.259009009009009</v>
+        <v>0.257730474835738</v>
       </c>
     </row>
     <row r="5">
@@ -494,7 +494,7 @@
         <v>0.05</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2516426200636727</v>
+        <v>0.2510668563300142</v>
       </c>
     </row>
     <row r="6">
@@ -507,7 +507,7 @@
         <v>0.05</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2557745715640452</v>
+        <v>0.2541996884102147</v>
       </c>
     </row>
     <row r="7">
@@ -520,7 +520,7 @@
         <v>0.05</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2525147327778907</v>
+        <v>0.2551480051480052</v>
       </c>
     </row>
     <row r="8">
@@ -533,7 +533,7 @@
         <v>0.05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2516172187224819</v>
+        <v>0.2510668563300142</v>
       </c>
     </row>
     <row r="9">
@@ -546,7 +546,7 @@
         <v>0.05</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2517526925421662</v>
+        <v>0.2505672966199282</v>
       </c>
     </row>
     <row r="10">
@@ -559,7 +559,7 @@
         <v>0.05</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2517526925421662</v>
+        <v>0.2508297771455666</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
         <v>0.05</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2517526925421662</v>
+        <v>0.2506096321885796</v>
       </c>
     </row>
     <row r="12">
@@ -611,7 +611,7 @@
         <v>0.1</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2342342342342342</v>
+        <v>0.2338946088946089</v>
       </c>
     </row>
     <row r="15">
@@ -624,7 +624,7 @@
         <v>0.1</v>
       </c>
       <c r="C15" t="n">
-        <v>0.221989846989847</v>
+        <v>0.2297118547118547</v>
       </c>
     </row>
     <row r="16">
@@ -637,7 +637,7 @@
         <v>0.1</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2348956098956099</v>
+        <v>0.2348241098241098</v>
       </c>
     </row>
     <row r="17">
@@ -650,7 +650,7 @@
         <v>0.1</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2274059774059774</v>
+        <v>0.2298012298012298</v>
       </c>
     </row>
     <row r="18">
@@ -663,7 +663,7 @@
         <v>0.1</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2236164736164736</v>
+        <v>0.2297118547118547</v>
       </c>
     </row>
     <row r="19">
@@ -676,7 +676,7 @@
         <v>0.1</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2238667238667239</v>
+        <v>0.2285678535678536</v>
       </c>
     </row>
     <row r="20">
@@ -689,7 +689,7 @@
         <v>0.1</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2238667238667239</v>
+        <v>0.2292113542113542</v>
       </c>
     </row>
     <row r="21">
@@ -702,7 +702,7 @@
         <v>0.1</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2238667238667239</v>
+        <v>0.2290862290862291</v>
       </c>
     </row>
     <row r="22">
@@ -741,7 +741,7 @@
         <v>0.15</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2132163676281323</v>
+        <v>0.2178155045802104</v>
       </c>
     </row>
     <row r="25">
@@ -754,7 +754,7 @@
         <v>0.15</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2002990385343327</v>
+        <v>0.2125634037398743</v>
       </c>
     </row>
     <row r="26">
@@ -767,7 +767,7 @@
         <v>0.15</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2140869861458096</v>
+        <v>0.2134813384813385</v>
       </c>
     </row>
     <row r="27">
@@ -780,7 +780,7 @@
         <v>0.15</v>
       </c>
       <c r="C27" t="n">
-        <v>0.203232644409115</v>
+        <v>0.207462714815656</v>
       </c>
     </row>
     <row r="28">
@@ -793,7 +793,7 @@
         <v>0.15</v>
       </c>
       <c r="C28" t="n">
-        <v>0.2015197971080324</v>
+        <v>0.2125634037398743</v>
       </c>
     </row>
     <row r="29">
@@ -806,7 +806,7 @@
         <v>0.15</v>
       </c>
       <c r="C29" t="n">
-        <v>0.2013494587023999</v>
+        <v>0.2128094481035658</v>
       </c>
     </row>
     <row r="30">
@@ -819,7 +819,7 @@
         <v>0.15</v>
       </c>
       <c r="C30" t="n">
-        <v>0.201377848436672</v>
+        <v>0.2127526686350216</v>
       </c>
     </row>
     <row r="31">
@@ -832,7 +832,7 @@
         <v>0.15</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2013494587023999</v>
+        <v>0.2129513967749262</v>
       </c>
     </row>
     <row r="32">
@@ -871,7 +871,7 @@
         <v>0.2</v>
       </c>
       <c r="C34" t="n">
-        <v>0.1946187258687259</v>
+        <v>0.2013352638352638</v>
       </c>
     </row>
     <row r="35">
@@ -884,7 +884,7 @@
         <v>0.2</v>
       </c>
       <c r="C35" t="n">
-        <v>0.1781692406692407</v>
+        <v>0.194980694980695</v>
       </c>
     </row>
     <row r="36">
@@ -897,7 +897,7 @@
         <v>0.2</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1952220077220077</v>
+        <v>0.1969916344916345</v>
       </c>
     </row>
     <row r="37">
@@ -910,7 +910,7 @@
         <v>0.2</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1842020592020592</v>
+        <v>0.1895913770913771</v>
       </c>
     </row>
     <row r="38">
@@ -923,7 +923,7 @@
         <v>0.2</v>
       </c>
       <c r="C38" t="n">
-        <v>0.1786518661518662</v>
+        <v>0.194980694980695</v>
       </c>
     </row>
     <row r="39">
@@ -936,7 +936,7 @@
         <v>0.2</v>
       </c>
       <c r="C39" t="n">
-        <v>0.1774050836550836</v>
+        <v>0.1940958815958816</v>
       </c>
     </row>
     <row r="40">
@@ -949,7 +949,7 @@
         <v>0.2</v>
       </c>
       <c r="C40" t="n">
-        <v>0.1773648648648649</v>
+        <v>0.1948198198198198</v>
       </c>
     </row>
     <row r="41">
@@ -962,7 +962,7 @@
         <v>0.2</v>
       </c>
       <c r="C41" t="n">
-        <v>0.1773648648648649</v>
+        <v>0.194015444015444</v>
       </c>
     </row>
     <row r="42">
@@ -1001,7 +1001,7 @@
         <v>0.25</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1822715572715573</v>
+        <v>0.1836658086658087</v>
       </c>
     </row>
     <row r="45">
@@ -1014,7 +1014,7 @@
         <v>0.25</v>
       </c>
       <c r="C45" t="n">
-        <v>0.15503003003003</v>
+        <v>0.1763191763191763</v>
       </c>
     </row>
     <row r="46">
@@ -1027,7 +1027,7 @@
         <v>0.25</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1823788073788074</v>
+        <v>0.1851673101673102</v>
       </c>
     </row>
     <row r="47">
@@ -1040,7 +1040,7 @@
         <v>0.25</v>
       </c>
       <c r="C47" t="n">
-        <v>0.1696696696696697</v>
+        <v>0.1770699270699271</v>
       </c>
     </row>
     <row r="48">
@@ -1053,7 +1053,7 @@
         <v>0.25</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1564242814242814</v>
+        <v>0.1763191763191763</v>
       </c>
     </row>
     <row r="49">
@@ -1066,7 +1066,7 @@
         <v>0.25</v>
       </c>
       <c r="C49" t="n">
-        <v>0.1561025311025311</v>
+        <v>0.1773916773916774</v>
       </c>
     </row>
     <row r="50">
@@ -1079,7 +1079,7 @@
         <v>0.25</v>
       </c>
       <c r="C50" t="n">
-        <v>0.155995280995281</v>
+        <v>0.1772844272844273</v>
       </c>
     </row>
     <row r="51">
@@ -1092,7 +1092,7 @@
         <v>0.25</v>
       </c>
       <c r="C51" t="n">
-        <v>0.155941655941656</v>
+        <v>0.177016302016302</v>
       </c>
     </row>
     <row r="52">
@@ -1131,7 +1131,7 @@
         <v>0.3</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1672412208126494</v>
+        <v>0.1716997609854753</v>
       </c>
     </row>
     <row r="55">
@@ -1144,7 +1144,7 @@
         <v>0.3</v>
       </c>
       <c r="C55" t="n">
-        <v>0.1251378929950359</v>
+        <v>0.1615186615186615</v>
       </c>
     </row>
     <row r="56">
@@ -1157,7 +1157,7 @@
         <v>0.3</v>
       </c>
       <c r="C56" t="n">
-        <v>0.1652877367163081</v>
+        <v>0.1698611877183306</v>
       </c>
     </row>
     <row r="57">
@@ -1170,7 +1170,7 @@
         <v>0.3</v>
       </c>
       <c r="C57" t="n">
-        <v>0.1575427468284611</v>
+        <v>0.1637709137709137</v>
       </c>
     </row>
     <row r="58">
@@ -1183,7 +1183,7 @@
         <v>0.3</v>
       </c>
       <c r="C58" t="n">
-        <v>0.1271833057547343</v>
+        <v>0.1615186615186615</v>
       </c>
     </row>
     <row r="59">
@@ -1196,7 +1196,7 @@
         <v>0.3</v>
       </c>
       <c r="C59" t="n">
-        <v>0.125298768155911</v>
+        <v>0.1619323405037691</v>
       </c>
     </row>
     <row r="60">
@@ -1209,7 +1209,7 @@
         <v>0.3</v>
       </c>
       <c r="C60" t="n">
-        <v>0.125298768155911</v>
+        <v>0.1624839124839125</v>
       </c>
     </row>
     <row r="61">
@@ -1222,7 +1222,7 @@
         <v>0.3</v>
       </c>
       <c r="C61" t="n">
-        <v>0.125298768155911</v>
+        <v>0.1626218054789483</v>
       </c>
     </row>
     <row r="62">
@@ -1261,7 +1261,7 @@
         <v>0.35</v>
       </c>
       <c r="C64" t="n">
-        <v>0.1561602811602812</v>
+        <v>0.1612464112464113</v>
       </c>
     </row>
     <row r="65">
@@ -1274,7 +1274,7 @@
         <v>0.35</v>
       </c>
       <c r="C65" t="n">
-        <v>0.09486684486684487</v>
+        <v>0.1477700227700228</v>
       </c>
     </row>
     <row r="66">
@@ -1287,7 +1287,7 @@
         <v>0.35</v>
       </c>
       <c r="C66" t="n">
-        <v>0.1468171468171468</v>
+        <v>0.1607885357885358</v>
       </c>
     </row>
     <row r="67">
@@ -1300,7 +1300,7 @@
         <v>0.35</v>
       </c>
       <c r="C67" t="n">
-        <v>0.1420527670527671</v>
+        <v>0.1539204039204039</v>
       </c>
     </row>
     <row r="68">
@@ -1313,7 +1313,7 @@
         <v>0.35</v>
       </c>
       <c r="C68" t="n">
-        <v>0.09622809622809624</v>
+        <v>0.1477700227700228</v>
       </c>
     </row>
     <row r="69">
@@ -1326,7 +1326,7 @@
         <v>0.35</v>
       </c>
       <c r="C69" t="n">
-        <v>0.0961785961785962</v>
+        <v>0.1470398970398971</v>
       </c>
     </row>
     <row r="70">
@@ -1339,7 +1339,7 @@
         <v>0.35</v>
       </c>
       <c r="C70" t="n">
-        <v>0.09610434610434609</v>
+        <v>0.1482526482526483</v>
       </c>
     </row>
     <row r="71">
@@ -1352,7 +1352,7 @@
         <v>0.35</v>
       </c>
       <c r="C71" t="n">
-        <v>0.09633947133947135</v>
+        <v>0.1478566478566479</v>
       </c>
     </row>
     <row r="72">
@@ -1391,7 +1391,7 @@
         <v>0.4</v>
       </c>
       <c r="C74" t="n">
-        <v>0.1397468897468898</v>
+        <v>0.1533676533676534</v>
       </c>
     </row>
     <row r="75">
@@ -1404,7 +1404,7 @@
         <v>0.4</v>
       </c>
       <c r="C75" t="n">
-        <v>0.06703131703131704</v>
+        <v>0.1343843843843844</v>
       </c>
     </row>
     <row r="76">
@@ -1417,7 +1417,7 @@
         <v>0.4</v>
       </c>
       <c r="C76" t="n">
-        <v>0.1342235092235092</v>
+        <v>0.1488095238095238</v>
       </c>
     </row>
     <row r="77">
@@ -1430,7 +1430,7 @@
         <v>0.4</v>
       </c>
       <c r="C77" t="n">
-        <v>0.1290755040755041</v>
+        <v>0.1433933933933934</v>
       </c>
     </row>
     <row r="78">
@@ -1443,7 +1443,7 @@
         <v>0.4</v>
       </c>
       <c r="C78" t="n">
-        <v>0.06665594165594166</v>
+        <v>0.1343843843843844</v>
       </c>
     </row>
     <row r="79">
@@ -1456,7 +1456,7 @@
         <v>0.4</v>
       </c>
       <c r="C79" t="n">
-        <v>0.06601244101244103</v>
+        <v>0.1345452595452595</v>
       </c>
     </row>
     <row r="80">
@@ -1469,7 +1469,7 @@
         <v>0.4</v>
       </c>
       <c r="C80" t="n">
-        <v>0.06601244101244103</v>
+        <v>0.1345988845988846</v>
       </c>
     </row>
     <row r="81">
@@ -1482,7 +1482,7 @@
         <v>0.4</v>
       </c>
       <c r="C81" t="n">
-        <v>0.06601244101244103</v>
+        <v>0.1345988845988846</v>
       </c>
     </row>
     <row r="82">
@@ -1521,7 +1521,7 @@
         <v>0.45</v>
       </c>
       <c r="C84" t="n">
-        <v>0.128978003978004</v>
+        <v>0.146966771966772</v>
       </c>
     </row>
     <row r="85">
@@ -1534,7 +1534,7 @@
         <v>0.45</v>
       </c>
       <c r="C85" t="n">
-        <v>0.05036855036855038</v>
+        <v>0.1217678717678718</v>
       </c>
     </row>
     <row r="86">
@@ -1547,7 +1547,7 @@
         <v>0.45</v>
       </c>
       <c r="C86" t="n">
-        <v>0.1293728793728794</v>
+        <v>0.1411606411606412</v>
       </c>
     </row>
     <row r="87">
@@ -1560,7 +1560,7 @@
         <v>0.45</v>
       </c>
       <c r="C87" t="n">
-        <v>0.1172779922779923</v>
+        <v>0.1326927576927577</v>
       </c>
     </row>
     <row r="88">
@@ -1573,7 +1573,7 @@
         <v>0.45</v>
       </c>
       <c r="C88" t="n">
-        <v>0.04777992277992279</v>
+        <v>0.1217678717678718</v>
       </c>
     </row>
     <row r="89">
@@ -1586,7 +1586,7 @@
         <v>0.45</v>
       </c>
       <c r="C89" t="n">
-        <v>0.04624429624429625</v>
+        <v>0.1207587457587458</v>
       </c>
     </row>
     <row r="90">
@@ -1599,7 +1599,7 @@
         <v>0.45</v>
       </c>
       <c r="C90" t="n">
-        <v>0.04624429624429625</v>
+        <v>0.120963495963496</v>
       </c>
     </row>
     <row r="91">
@@ -1612,7 +1612,7 @@
         <v>0.45</v>
       </c>
       <c r="C91" t="n">
-        <v>0.04624429624429625</v>
+        <v>0.120978120978121</v>
       </c>
     </row>
     <row r="92">
@@ -1651,7 +1651,7 @@
         <v>0.4999999999999999</v>
       </c>
       <c r="C94" t="n">
-        <v>0.1148648648648649</v>
+        <v>0.13497425997426</v>
       </c>
     </row>
     <row r="95">
@@ -1664,7 +1664,7 @@
         <v>0.4999999999999999</v>
       </c>
       <c r="C95" t="n">
-        <v>0.03072715572715573</v>
+        <v>0.1082689832689833</v>
       </c>
     </row>
     <row r="96">
@@ -1677,7 +1677,7 @@
         <v>0.4999999999999999</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1174388674388674</v>
+        <v>0.1296653796653797</v>
       </c>
     </row>
     <row r="97">
@@ -1690,7 +1690,7 @@
         <v>0.4999999999999999</v>
       </c>
       <c r="C97" t="n">
-        <v>0.1037644787644788</v>
+        <v>0.1243564993564994</v>
       </c>
     </row>
     <row r="98">
@@ -1703,7 +1703,7 @@
         <v>0.4999999999999999</v>
       </c>
       <c r="C98" t="n">
-        <v>0.03104890604890605</v>
+        <v>0.1082689832689833</v>
       </c>
     </row>
     <row r="99">
@@ -1716,7 +1716,7 @@
         <v>0.4999999999999999</v>
       </c>
       <c r="C99" t="n">
-        <v>0.03120978120978122</v>
+        <v>0.1076254826254826</v>
       </c>
     </row>
     <row r="100">
@@ -1729,7 +1729,7 @@
         <v>0.4999999999999999</v>
       </c>
       <c r="C100" t="n">
-        <v>0.03104890604890605</v>
+        <v>0.1076254826254826</v>
       </c>
     </row>
     <row r="101">
@@ -1742,7 +1742,7 @@
         <v>0.4999999999999999</v>
       </c>
       <c r="C101" t="n">
-        <v>0.03137065637065638</v>
+        <v>0.1077863577863578</v>
       </c>
     </row>
     <row r="102">
@@ -1781,7 +1781,7 @@
         <v>0.5499999999999999</v>
       </c>
       <c r="C104" t="n">
-        <v>0.1028886028886029</v>
+        <v>0.1243743743743744</v>
       </c>
     </row>
     <row r="105">
@@ -1794,7 +1794,7 @@
         <v>0.5499999999999999</v>
       </c>
       <c r="C105" t="n">
-        <v>0.01644501644501646</v>
+        <v>0.09856284856284858</v>
       </c>
     </row>
     <row r="106">
@@ -1807,7 +1807,7 @@
         <v>0.5499999999999999</v>
       </c>
       <c r="C106" t="n">
-        <v>0.1043186043186043</v>
+        <v>0.1162591162591163</v>
       </c>
     </row>
     <row r="107">
@@ -1820,7 +1820,7 @@
         <v>0.5499999999999999</v>
       </c>
       <c r="C107" t="n">
-        <v>0.09706134706134709</v>
+        <v>0.1148112398112398</v>
       </c>
     </row>
     <row r="108">
@@ -1833,7 +1833,7 @@
         <v>0.5499999999999999</v>
       </c>
       <c r="C108" t="n">
-        <v>0.01397826397826398</v>
+        <v>0.09856284856284858</v>
       </c>
     </row>
     <row r="109">
@@ -1846,7 +1846,7 @@
         <v>0.5499999999999999</v>
       </c>
       <c r="C109" t="n">
-        <v>0.01356713856713858</v>
+        <v>0.09516659516659517</v>
       </c>
     </row>
     <row r="110">
@@ -1859,7 +1859,7 @@
         <v>0.5499999999999999</v>
       </c>
       <c r="C110" t="n">
-        <v>0.01340626340626342</v>
+        <v>0.09673959673959676</v>
       </c>
     </row>
     <row r="111">
@@ -1872,7 +1872,7 @@
         <v>0.5499999999999999</v>
       </c>
       <c r="C111" t="n">
-        <v>0.01340626340626342</v>
+        <v>0.09613184613184614</v>
       </c>
     </row>
     <row r="112">
@@ -1911,7 +1911,7 @@
         <v>0.6</v>
       </c>
       <c r="C114" t="n">
-        <v>0.0863899613899614</v>
+        <v>0.1138191763191763</v>
       </c>
     </row>
     <row r="115">
@@ -1924,7 +1924,7 @@
         <v>0.6</v>
       </c>
       <c r="C115" t="n">
-        <v>0.004826254826254827</v>
+        <v>0.08397683397683398</v>
       </c>
     </row>
     <row r="116">
@@ -1937,7 +1937,7 @@
         <v>0.6</v>
       </c>
       <c r="C116" t="n">
-        <v>0.08204633204633205</v>
+        <v>0.1012709137709138</v>
       </c>
     </row>
     <row r="117">
@@ -1950,7 +1950,7 @@
         <v>0.6</v>
       </c>
       <c r="C117" t="n">
-        <v>0.08968790218790218</v>
+        <v>0.1077059202059202</v>
       </c>
     </row>
     <row r="118">
@@ -1963,7 +1963,7 @@
         <v>0.6</v>
       </c>
       <c r="C118" t="n">
-        <v>0.002815315315315318</v>
+        <v>0.08397683397683398</v>
       </c>
     </row>
     <row r="119">
@@ -1976,7 +1976,7 @@
         <v>0.6</v>
       </c>
       <c r="C119" t="n">
-        <v>0.002413127413127419</v>
+        <v>0.08156370656370657</v>
       </c>
     </row>
     <row r="120">
@@ -1989,7 +1989,7 @@
         <v>0.6</v>
       </c>
       <c r="C120" t="n">
-        <v>0.002252252252252257</v>
+        <v>0.08325289575289577</v>
       </c>
     </row>
     <row r="121">
@@ -2002,7 +2002,7 @@
         <v>0.6</v>
       </c>
       <c r="C121" t="n">
-        <v>0.002252252252252257</v>
+        <v>0.0822876447876448</v>
       </c>
     </row>
     <row r="122">
@@ -2041,7 +2041,7 @@
         <v>0.65</v>
       </c>
       <c r="C124" t="n">
-        <v>0.07292241220812649</v>
+        <v>0.09696175767604338</v>
       </c>
     </row>
     <row r="125">
@@ -2054,7 +2054,7 @@
         <v>0.65</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.004251700680272114</v>
+        <v>0.07023349880492738</v>
       </c>
     </row>
     <row r="126">
@@ -2067,7 +2067,7 @@
         <v>0.65</v>
       </c>
       <c r="C126" t="n">
-        <v>0.06430410001838573</v>
+        <v>0.0877688913403199</v>
       </c>
     </row>
     <row r="127">
@@ -2080,7 +2080,7 @@
         <v>0.65</v>
       </c>
       <c r="C127" t="n">
-        <v>0.07986302629159772</v>
+        <v>0.09608843537414967</v>
       </c>
     </row>
     <row r="128">
@@ -2093,7 +2093,7 @@
         <v>0.65</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.005998345284059577</v>
+        <v>0.07023349880492738</v>
       </c>
     </row>
     <row r="129">
@@ -2106,7 +2106,7 @@
         <v>0.65</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.005561684133112706</v>
+        <v>0.065292333149476</v>
       </c>
     </row>
     <row r="130">
@@ -2119,7 +2119,7 @@
         <v>0.65</v>
       </c>
       <c r="C130" t="n">
-        <v>-0.005423791138076853</v>
+        <v>0.06740669240669239</v>
       </c>
     </row>
     <row r="131">
@@ -2132,7 +2132,7 @@
         <v>0.65</v>
       </c>
       <c r="C131" t="n">
-        <v>-0.005561684133112706</v>
+        <v>0.06641845927560214</v>
       </c>
     </row>
     <row r="132">
@@ -2171,7 +2171,7 @@
         <v>0.7</v>
       </c>
       <c r="C134" t="n">
-        <v>0.06376018876018877</v>
+        <v>0.08789146289146291</v>
       </c>
     </row>
     <row r="135">
@@ -2184,7 +2184,7 @@
         <v>0.7</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.007829257829257827</v>
+        <v>0.04606392106392107</v>
       </c>
     </row>
     <row r="136">
@@ -2197,7 +2197,7 @@
         <v>0.7</v>
       </c>
       <c r="C136" t="n">
-        <v>0.05662805662805664</v>
+        <v>0.07314457314457314</v>
       </c>
     </row>
     <row r="137">
@@ -2210,7 +2210,7 @@
         <v>0.7</v>
       </c>
       <c r="C137" t="n">
-        <v>0.07191119691119692</v>
+        <v>0.08526383526383527</v>
       </c>
     </row>
     <row r="138">
@@ -2223,7 +2223,7 @@
         <v>0.7</v>
       </c>
       <c r="C138" t="n">
-        <v>-0.009062634062634058</v>
+        <v>0.04606392106392107</v>
       </c>
     </row>
     <row r="139">
@@ -2236,7 +2236,7 @@
         <v>0.7</v>
       </c>
       <c r="C139" t="n">
-        <v>-0.00788288288288288</v>
+        <v>0.04172029172029172</v>
       </c>
     </row>
     <row r="140">
@@ -2249,7 +2249,7 @@
         <v>0.7</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.00788288288288288</v>
+        <v>0.04273916773916775</v>
       </c>
     </row>
     <row r="141">
@@ -2262,7 +2262,7 @@
         <v>0.7</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.00788288288288288</v>
+        <v>0.04284641784641785</v>
       </c>
     </row>
     <row r="142">
@@ -2301,7 +2301,7 @@
         <v>0.75</v>
       </c>
       <c r="C144" t="n">
-        <v>0.05405405405405406</v>
+        <v>0.07673745173745174</v>
       </c>
     </row>
     <row r="145">
@@ -2314,7 +2314,7 @@
         <v>0.75</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.007239382239382239</v>
+        <v>0.02139639639639639</v>
       </c>
     </row>
     <row r="146">
@@ -2327,7 +2327,7 @@
         <v>0.75</v>
       </c>
       <c r="C146" t="n">
-        <v>0.04311454311454311</v>
+        <v>0.05196267696267697</v>
       </c>
     </row>
     <row r="147">
@@ -2340,7 +2340,7 @@
         <v>0.75</v>
       </c>
       <c r="C147" t="n">
-        <v>0.05791505791505792</v>
+        <v>0.07722007722007723</v>
       </c>
     </row>
     <row r="148">
@@ -2353,7 +2353,7 @@
         <v>0.75</v>
       </c>
       <c r="C148" t="n">
-        <v>-0.01045688545688546</v>
+        <v>0.02139639639639639</v>
       </c>
     </row>
     <row r="149">
@@ -2366,7 +2366,7 @@
         <v>0.75</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.00756113256113256</v>
+        <v>0.01721364221364222</v>
       </c>
     </row>
     <row r="150">
@@ -2379,7 +2379,7 @@
         <v>0.75</v>
       </c>
       <c r="C150" t="n">
-        <v>-0.00756113256113256</v>
+        <v>0.01817889317889318</v>
       </c>
     </row>
     <row r="151">
@@ -2392,7 +2392,7 @@
         <v>0.75</v>
       </c>
       <c r="C151" t="n">
-        <v>-0.00756113256113256</v>
+        <v>0.01721364221364222</v>
       </c>
     </row>
     <row r="152">
@@ -2431,7 +2431,7 @@
         <v>0.7999999999999999</v>
       </c>
       <c r="C154" t="n">
-        <v>0.0390926640926641</v>
+        <v>0.05807593307593309</v>
       </c>
     </row>
     <row r="155">
@@ -2444,7 +2444,7 @@
         <v>0.7999999999999999</v>
       </c>
       <c r="C155" t="n">
-        <v>-0.007078507078507075</v>
+        <v>0.003056628056628072</v>
       </c>
     </row>
     <row r="156">
@@ -2457,7 +2457,7 @@
         <v>0.7999999999999999</v>
       </c>
       <c r="C156" t="n">
-        <v>0.004021879021879022</v>
+        <v>0.03410553410553411</v>
       </c>
     </row>
     <row r="157">
@@ -2470,7 +2470,7 @@
         <v>0.7999999999999999</v>
       </c>
       <c r="C157" t="n">
-        <v>0.04295366795366797</v>
+        <v>0.06097168597168598</v>
       </c>
     </row>
     <row r="158">
@@ -2483,7 +2483,7 @@
         <v>0.7999999999999999</v>
       </c>
       <c r="C158" t="n">
-        <v>-0.00836550836550836</v>
+        <v>0.003056628056628072</v>
       </c>
     </row>
     <row r="159">
@@ -2496,7 +2496,7 @@
         <v>0.7999999999999999</v>
       </c>
       <c r="C159" t="n">
-        <v>-0.00852638352638352</v>
+        <v>-0.0006435006435006295</v>
       </c>
     </row>
     <row r="160">
@@ -2509,7 +2509,7 @@
         <v>0.7999999999999999</v>
       </c>
       <c r="C160" t="n">
-        <v>-0.00852638352638352</v>
+        <v>0.0008043758043758155</v>
       </c>
     </row>
     <row r="161">
@@ -2522,7 +2522,7 @@
         <v>0.7999999999999999</v>
       </c>
       <c r="C161" t="n">
-        <v>-0.00852638352638352</v>
+        <v>-0.0001608751608751478</v>
       </c>
     </row>
     <row r="162">
@@ -2561,7 +2561,7 @@
         <v>0.85</v>
       </c>
       <c r="C164" t="n">
-        <v>0.01678464178464179</v>
+        <v>0.03464178464178464</v>
       </c>
     </row>
     <row r="165">
@@ -2574,7 +2574,7 @@
         <v>0.85</v>
       </c>
       <c r="C165" t="n">
-        <v>-0.004826254826254826</v>
+        <v>-0.01083226083226083</v>
       </c>
     </row>
     <row r="166">
@@ -2600,7 +2600,7 @@
         <v>0.85</v>
       </c>
       <c r="C167" t="n">
-        <v>0.03040540540540541</v>
+        <v>0.04622479622479623</v>
       </c>
     </row>
     <row r="168">
@@ -2613,7 +2613,7 @@
         <v>0.85</v>
       </c>
       <c r="C168" t="n">
-        <v>-0.0074002574002574</v>
+        <v>-0.01083226083226083</v>
       </c>
     </row>
     <row r="169">
@@ -2626,7 +2626,7 @@
         <v>0.85</v>
       </c>
       <c r="C169" t="n">
-        <v>-0.005737880737880737</v>
+        <v>-0.01093951093951094</v>
       </c>
     </row>
     <row r="170">
@@ -2639,7 +2639,7 @@
         <v>0.85</v>
       </c>
       <c r="C170" t="n">
-        <v>-0.005737880737880737</v>
+        <v>-0.01061776061776062</v>
       </c>
     </row>
     <row r="171">
@@ -2652,7 +2652,7 @@
         <v>0.85</v>
       </c>
       <c r="C171" t="n">
-        <v>-0.005737880737880737</v>
+        <v>-0.01061776061776062</v>
       </c>
     </row>
     <row r="172">
@@ -2691,7 +2691,7 @@
         <v>0.9</v>
       </c>
       <c r="C174" t="n">
-        <v>0.0004826254826254826</v>
+        <v>0.0102960102960103</v>
       </c>
     </row>
     <row r="175">
@@ -2704,7 +2704,7 @@
         <v>0.9</v>
       </c>
       <c r="C175" t="n">
-        <v>-0.004182754182754184</v>
+        <v>-0.01914414414414415</v>
       </c>
     </row>
     <row r="176">
@@ -2730,7 +2730,7 @@
         <v>0.9</v>
       </c>
       <c r="C177" t="n">
-        <v>0.01447876447876448</v>
+        <v>0.02927927927927927</v>
       </c>
     </row>
     <row r="178">
@@ -2743,7 +2743,7 @@
         <v>0.9</v>
       </c>
       <c r="C178" t="n">
-        <v>-0.004182754182754184</v>
+        <v>-0.01914414414414415</v>
       </c>
     </row>
     <row r="179">
@@ -2756,7 +2756,7 @@
         <v>0.9</v>
       </c>
       <c r="C179" t="n">
-        <v>-0.004182754182754184</v>
+        <v>-0.01817889317889318</v>
       </c>
     </row>
     <row r="180">
@@ -2769,7 +2769,7 @@
         <v>0.9</v>
       </c>
       <c r="C180" t="n">
-        <v>-0.004182754182754184</v>
+        <v>-0.01817889317889318</v>
       </c>
     </row>
     <row r="181">
@@ -2782,7 +2782,7 @@
         <v>0.9</v>
       </c>
       <c r="C181" t="n">
-        <v>-0.004182754182754184</v>
+        <v>-0.01817889317889318</v>
       </c>
     </row>
     <row r="182">
@@ -2834,7 +2834,7 @@
         <v>0.95</v>
       </c>
       <c r="C185" t="n">
-        <v>-0.003056628056628054</v>
+        <v>-0.02010939510939509</v>
       </c>
     </row>
     <row r="186">
@@ -2860,7 +2860,7 @@
         <v>0.95</v>
       </c>
       <c r="C187" t="n">
-        <v>-0.002895752895752873</v>
+        <v>0.003217503217503248</v>
       </c>
     </row>
     <row r="188">
@@ -2873,7 +2873,7 @@
         <v>0.95</v>
       </c>
       <c r="C188" t="n">
-        <v>-0.003056628056628054</v>
+        <v>-0.02010939510939509</v>
       </c>
     </row>
     <row r="189">
@@ -2886,7 +2886,7 @@
         <v>0.95</v>
       </c>
       <c r="C189" t="n">
-        <v>0</v>
+        <v>-0.01994851994851993</v>
       </c>
     </row>
     <row r="190">
@@ -2899,7 +2899,7 @@
         <v>0.95</v>
       </c>
       <c r="C190" t="n">
-        <v>0</v>
+        <v>-0.01994851994851993</v>
       </c>
     </row>
     <row r="191">
@@ -2912,7 +2912,7 @@
         <v>0.95</v>
       </c>
       <c r="C191" t="n">
-        <v>0</v>
+        <v>-0.01994851994851993</v>
       </c>
     </row>
   </sheetData>

--- a/RESULTS/tables/decision_curve_external_validation.xlsx
+++ b/RESULTS/tables/decision_curve_external_validation.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,17 +417,17 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Threshold</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Net Benefit</t>
         </is>
